--- a/human_validation/judge/kor/judge_D016_S004_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S004_P001__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,145 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 제 이름은 리 선생님입니다 — 오늘 함께 이야기 나눌게요. 먼저, 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 하루 중 너무 많은 시간을 뭔가 확인하는 데 쓰고 있어서 왔어요. 중요한 서류와 소중한 물건들이 제가 놔둔 자리에 그대로 있는지 확인하려고, 몇 분 전에 확인했는데도 같은 폴더, 서랍, 라벨 붙인 상자들을 계속 열어봐요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 이렇게 반복적으로 확인하실 때, 그게 원치 않는데도 자꾸 드는 충동처럼 느껴져서 멈추고 싶으신가요, 아니면 정리 상태를 유지하기 위해 꼭 필요한 올바른 행동이라고 느껴지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 해야만 하는 일처럼 느껴져요, 방금 봤다는 걸 알면서도요. 폴더와 서랍을 계속 다시 열고, 상자들을 또 확인하는데, 그게 하루 중 너무 많은 시간을 잡아먹어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 다시 확인하러 가실 때, 확인하지 않으면 뭔가 안 좋은 일이 일어날 것 같은 성가신 생각이나 두려움 때문인가요, 아니면 정말로 이미 확인했는지 안 했는지 기억이 안 나서인가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 성가신 생각 쪽에 더 가까워요. '남편의 오래된 세금 서류를 버린 건 아닐까?' 아니면 가족 요리법 중 하나를 잘못된 상자에 넣은 건 아닐까 하는 생각이 들어요. 그게 아마 사실이 아니라는 걸 알면서도, 다시 돌아가서 확인할 때까지는 제가 정말 부주의했다는 느낌이 끔찍하게 들어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 이런 확인하고 싶은 충동과 그 뒤에 있는 생각들이 상당한 고통을 주거나 매일 많은 시간을 잡아먹나요, 아니면 삶의 여러 다른 영역에 대해 걱정하는 더 넓은 패턴의 한 부분이라고 말씀하시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 정말 많은 시간을 잡아먹어요. 오후 시간을 통째로 확인하느라 날려버려서 멘토링 세션을 취소하고 독서 모임을 놓친 적도 있어요. 그리고 아파트가 여전히 정리가 안 된 상태라 누군가를 초대하기가 민망해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 서류나 소중한 물건을 확인하는 것 외에, 더 이상 필요 없는 물건들을 버리거나 처분하는 게, 실용적인 가치가 거의 없는 것들이라도, 아주 어렵게 느껴지시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 그게 진짜 문제인지는 잘 모르겠어요. 몇몇 물건은 계속 가지고 있긴 한데, 필요 없는 걸 못 버린다는 느낌은 특별히 받은 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 다시 돌아가서 확인하고 싶은 충동이 들 때, 힘들더라도 그걸 참거나 멈추려고 해보신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 그러려고 노력은 해요, 특히 몇 분 전에 확인했을 때는요. 그런데 너무 불안해져서 결국 폴더와 서랍을 또 열게 돼요, 모든 게 제가 놔둔 자리에 그대로 있는지 확인하려고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 강박장애 (D016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진단명: 강박장애 (D016)
 인구통계: 성별 여성 / 나이 86 / 직업상태 not in workforce / 최종학력 학사
@@ -575,194 +705,31 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S066
-배경 서술: 아난타 카디르가 오랫동안 살던 가족의 집에서 배링턴 근처의 노인 친화적인 작은 아파트로 이사하면서, 수십 년간 쌓인 장부와 요리법, 미술 재료, 가족 대대로 내려온 물건들을 정리하는 일이 예전에는 그저 꼼꼼한 성격처럼 보였던 습관에 새로운 강도를 더했다. 중요한 서류를 잘못 두었거나 가족 유품을 소홀히 다뤘을지도 모른다는 침투적이고 원치 않는 걱정 때문에 그녀는 반복적으로 확인하고 재확인하는 일과에 빠져들었고, 이는 점점 그녀의 멘토링 워크숍, 독서 모임 약속, 명절 요리 준비를 밀어내게 되었다. 커뮤니티 센터의 몇몇 마감을 놓치고, 아파트가 결코 정돈된 느낌이 들지 않는다는 이유로 방문객을 피하기 시작하면서 이 문제는 임상적으로 유의미해졌다. 담당 1차 진료의는 정기 진료 중 이런 변화를 알아챘고, 아난타가 하루 대부분이 이런 반복적인 행동을 중심으로 짜여 있다고 설명하자 그녀를 노인정신과 전문의에게 의뢰했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 제 이름은 리 선생님입니다 — 오늘 함께 이야기 나눌게요. 먼저, 오늘 저를 찾아오시게 된 이유를 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 하루 중 너무 많은 시간을 뭔가 확인하는 데 쓰고 있어서 왔어요. 중요한 서류와 소중한 물건들이 제가 놔둔 자리에 그대로 있는지 확인하려고, 몇 분 전에 확인했는데도 같은 폴더, 서랍, 라벨 붙인 상자들을 계속 열어봐요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 이렇게 반복적으로 확인하실 때, 그게 원치 않는데도 자꾸 드는 충동처럼 느껴져서 멈추고 싶으신가요, 아니면 정리 상태를 유지하기 위해 꼭 필요한 올바른 행동이라고 느껴지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 해야만 하는 일처럼 느껴져요, 방금 봤다는 걸 알면서도요. 폴더와 서랍을 계속 다시 열고, 상자들을 또 확인하는데, 그게 하루 중 너무 많은 시간을 잡아먹어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 다시 확인하러 가실 때, 확인하지 않으면 뭔가 안 좋은 일이 일어날 것 같은 성가신 생각이나 두려움 때문인가요, 아니면 정말로 이미 확인했는지 안 했는지 기억이 안 나서인가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 성가신 생각 쪽에 더 가까워요. '남편의 오래된 세금 서류를 버린 건 아닐까?' 아니면 가족 요리법 중 하나를 잘못된 상자에 넣은 건 아닐까 하는 생각이 들어요. 그게 아마 사실이 아니라는 걸 알면서도, 다시 돌아가서 확인할 때까지는 제가 정말 부주의했다는 느낌이 끔찍하게 들어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 이런 확인하고 싶은 충동과 그 뒤에 있는 생각들이 상당한 고통을 주거나 매일 많은 시간을 잡아먹나요, 아니면 삶의 여러 다른 영역에 대해 걱정하는 더 넓은 패턴의 한 부분이라고 말씀하시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 정말 많은 시간을 잡아먹어요. 오후 시간을 통째로 확인하느라 날려버려서 멘토링 세션을 취소하고 독서 모임을 놓친 적도 있어요. 그리고 아파트가 여전히 정리가 안 된 상태라 누군가를 초대하기가 민망해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 서류나 소중한 물건을 확인하는 것 외에, 더 이상 필요 없는 물건들을 버리거나 처분하는 게, 실용적인 가치가 거의 없는 것들이라도, 아주 어렵게 느껴지시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 그게 진짜 문제인지는 잘 모르겠어요. 몇몇 물건은 계속 가지고 있긴 한데, 필요 없는 걸 못 버린다는 느낌은 특별히 받은 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 다시 돌아가서 확인하고 싶은 충동이 들 때, 힘들더라도 그걸 참거나 멈추려고 해보신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 그러려고 노력은 해요, 특히 몇 분 전에 확인했을 때는요. 그런데 너무 불안해져서 결국 폴더와 서랍을 또 열게 돼요, 모든 게 제가 놔둔 자리에 그대로 있는지 확인하려고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+배경 서술: 아난타 카디르가 오랫동안 살던 가족의 집에서 배링턴 근처의 노인 친화적인 작은 아파트로 이사하면서, 수십 년간 쌓인 장부와 요리법, 미술 재료, 가족 대대로 내려온 물건들을 정리하는 일이 예전에는 그저 꼼꼼한 성격처럼 보였던 습관에 새로운 강도를 더했다. 중요한 서류를 잘못 두었거나 가족 유품을 소홀히 다뤘을지도 모른다는 침투적이고 원치 않는 걱정 때문에 그녀는 반복적으로 확인하고 재확인하는 일과에 빠져들었고, 이는 점점 그녀의 멘토링 워크숍, 독서 모임 약속, 명절 요리 준비를 밀어내게 되었다. 커뮤니티 센터의 몇몇 마감을 놓치고, 아파트가 결코 정돈된 느낌이 들지 않는다는 이유로 방문객을 피하기 시작하면서 이 문제는 임상적으로 유의미해졌다. 담당 1차 진료의는 정기 진료 중 이런 변화를 알아챘고, 아난타가 하루 대부분이 이런 반복적인 행동을 중심으로 짜여 있다고 설명하자 그녀를 노인정신과 전문의에게 의뢰했다.
+표집된 증상 목록:
+  - S065 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - S066 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 강박장애 (D016)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
-  확인된 근거: 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.; 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 강박장애 (D016, ICD: F42)
+지속 기간 요건: None
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: obsessive_compulsive_symptoms (관계=must_include, 요구개수=1, 충족개수=2, 커버리지=1.0)
+확인된 근거:
+  - 강박사고: 침투적이고 원치 않는 것으로 경험되는 반복적이고 지속적인 생각, 충동, 심상, 그리고 이를 무시하거나 억누르려는 시도.
+  - 강박행동: 강박사고에 대한 반응으로, 또는 불안/고통을 예방하기 위해 수행하는 반복적 행동이나 정신적 활동으로, 명백히 과도하거나 현실적으로 연관성이 없음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S004_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S004_P001__claude-sonnet-5_kor.xlsx
@@ -691,6 +691,11 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -725,11 +730,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D016_S004_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D016_S004_P001__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.2556</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
